--- a/order_forms/044_wallpaper_subscription_form--order_forms.xlsx
+++ b/order_forms/044_wallpaper_subscription_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>subscription_plan</t>
+          <t>subscription_plan_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Subscription Plan</t>
+          <t>Subscription Plan 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>billing_frequency</t>
+          <t>billing_frequency_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Billing Frequency</t>
+          <t>Billing Frequency 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>billing_date</t>
+          <t>billing_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Billing Date</t>
+          <t>Billing Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>billing_method</t>
+          <t>billing_method_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Billing Method</t>
+          <t>Billing Method 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>billing_address</t>
+          <t>billing_address_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Billing Address</t>
+          <t>Billing Address 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>subscription_plan_choices</t>
+          <t>subscription_plan_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>subscription_plan_choices</t>
+          <t>subscription_plan_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>billing_frequency_choices</t>
+          <t>billing_frequency_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>billing_frequency_choices</t>
+          <t>billing_frequency_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1537,7 +1537,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>billing_date_choices</t>
+          <t>billing_date_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>billing_date_choices</t>
+          <t>billing_date_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>billing_method_choices</t>
+          <t>billing_method_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>billing_method_choices</t>
+          <t>billing_method_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
